--- a/Weeks 5 & 6/regression_comparison.xlsx
+++ b/Weeks 5 & 6/regression_comparison.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/103d5954b5267379/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mcdw2\Documents\IDX_Clone\Weeks 5 &amp; 6\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{936288B9-92F2-4893-8DF5-445F25DEC717}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DFC9CB8-17A9-48D9-A8CD-F4BAF7AE0E33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{3D1BE86F-92DF-4CAD-BD51-8F714C03EB25}"/>
   </bookViews>
@@ -505,7 +505,7 @@
         <v>5</v>
       </c>
       <c r="E4">
-        <v>0.73029999999999995</v>
+        <v>0.71096527254466702</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -522,7 +522,7 @@
         <v>5</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0.90144013136509604</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -573,7 +573,7 @@
         <v>5</v>
       </c>
       <c r="E8">
-        <v>0.98280000000000001</v>
+        <v>0.70898564331274805</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
@@ -590,7 +590,7 @@
         <v>5</v>
       </c>
       <c r="E9">
-        <v>0.99960000000000004</v>
+        <v>0.86094774227156301</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -641,7 +641,7 @@
         <v>5</v>
       </c>
       <c r="E12">
-        <v>0.98780000000000001</v>
+        <v>0.80987214896156301</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -658,7 +658,7 @@
         <v>5</v>
       </c>
       <c r="E13">
-        <v>0.99970000000000003</v>
+        <v>0.92643313168425401</v>
       </c>
     </row>
   </sheetData>
